--- a/data_out/country_spreadsheets/Poland.xlsx
+++ b/data_out/country_spreadsheets/Poland.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>153.95</v>
       </c>
+      <c r="X2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>190.99</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>162.79</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>171.7</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>165.12</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>164.04</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>153.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>202.56</v>
       </c>
+      <c r="X3" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>168.97</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>84.72</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>195.37</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>134.98</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>202.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>223.51</v>
       </c>
+      <c r="X4" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>237.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>244.79</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>206.51</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110.44</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>223.51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>290.51</v>
       </c>
+      <c r="X5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>138.28</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>160.76</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>201.16</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>111.91</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>181.71</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>241.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>127.68</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>191.74</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>176.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>290.51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>212.07</v>
       </c>
+      <c r="X6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>111.76</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>143.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>127.86</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>107.81</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>131.22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>149.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>212.07</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>177.61</v>
       </c>
+      <c r="X7" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>189.92</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>161.96</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>159.72</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>209.74</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>195.02</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>128.81</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>177.61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>76.11</v>
       </c>
+      <c r="X8" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>193.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>217.29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>166.82</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>76.11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>147.53</v>
       </c>
+      <c r="X9" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>149.55</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>184</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>147.53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>17.76</v>
       </c>
+      <c r="X10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>186.96</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>277</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>245.36</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>207.84</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.76</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>71.84</v>
       </c>
+      <c r="X11" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>133.66</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>159.07</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>220.46</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>157.04</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>101.69</v>
       </c>
+      <c r="X12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>208.18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>157.75</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>101.69</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>48.26</v>
       </c>
+      <c r="X13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>178.24</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>237.43</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>162.59</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>94</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>48.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>75.31</v>
       </c>
+      <c r="X14" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>173.45</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>135.51</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>189.21</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>154.43</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>75.31</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>89.81</v>
       </c>
+      <c r="X15" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>171.65</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>169.31</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>233.39</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>132.61</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>105.57</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>89.81</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>79.03</v>
       </c>
+      <c r="X16" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>223.23</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>165.36</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>277.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>201.38</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>78.93000000000001</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>79.03</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>32.43</v>
       </c>
+      <c r="X17" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>264.01</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>221.79</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>150.34</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>198.58</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>107.17</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32.43</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>86.58</v>
       </c>
+      <c r="X18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>101.71</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>196.83</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>341.11</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>311.87</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>86.58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>8.68</v>
       </c>
+      <c r="X19" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>195.17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>203.05</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>137.54</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>161.03</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>207.87</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>108.36</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8.68</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>58.78</v>
       </c>
+      <c r="X20" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>147.58</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>189.47</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>317.7</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>264.02</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>91.29000000000001</v>
       </c>
+      <c r="X21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>118.28</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>193.32</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>339.49</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>261.66</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>203.35</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>135.61</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>91.29000000000001</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>160.06</v>
       </c>
+      <c r="X22" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>140.73</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>179.23</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>137.54</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>111.53</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>160.06</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>131.15</v>
       </c>
+      <c r="X23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>188.46</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>212.18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>194.92</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>180.64</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>131.15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>179.3</v>
       </c>
+      <c r="X24" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>123.13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>191.95</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>196.22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>122</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>179.3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>158.56</v>
       </c>
+      <c r="X25" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>192.21</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>190.64</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>261.23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>135.76</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>144.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>158.56</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>136.88</v>
       </c>
+      <c r="X26" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>162.48</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>291.47</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>136.88</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>35.98</v>
       </c>
+      <c r="X27" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>195.48</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>309.27</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>272.76</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>183.89</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>35.98</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>0</v>
       </c>
+      <c r="X28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>135.65</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>342.43</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>159.59</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>46.64</v>
       </c>
+      <c r="X29" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>149.93</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>218.07</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>296.95</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>177.65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>134.45</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>78.34</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>46.64</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>8.25</v>
       </c>
+      <c r="X30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>199.37</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>319.59</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>222.9</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>155.24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>102.12</v>
       </c>
+      <c r="X31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>195.1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>199.82</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>208.52</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>77.06</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>102.12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>7.16</v>
       </c>
+      <c r="X32" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>102.59</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>201.95</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>336.09</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>161.09</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>143.73</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>7.16</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>134.68</v>
       </c>
+      <c r="X33" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>198.83</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>197.86</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>226.33</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>130.26</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>134.68</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>173.51</v>
       </c>
+      <c r="X34" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>138.59</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>196.38</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>160.86</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>207.57</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>160.06</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>105.79</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>173.51</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>82.37</v>
       </c>
+      <c r="X35" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>135.85</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>306.97</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>186.18</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>281.43</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>82.37</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>116.25</v>
       </c>
+      <c r="X36" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>38.63</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>113.22</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>286.35</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>188.17</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>303.48</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>142.32</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>102.51</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>116.25</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>61.6</v>
       </c>
+      <c r="X37" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>260.45</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>185.03</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>102.68</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>61.6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>97.78</v>
       </c>
+      <c r="X38" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>108.54</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>277.82</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>172.55</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>143.13</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>201.21</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>248.7</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>197.25</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>97.78</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>125.08</v>
       </c>
+      <c r="X39" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>66.97</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>275.63</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>238.27</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>178.51</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>143.62</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>120.61</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>125.08</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>99.06</v>
       </c>
+      <c r="X40" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>255.97</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>125.94</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>109.92</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>173.85</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>110.33</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>99.06</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3624,6 +5698,57 @@
       <c r="W41" t="n">
         <v>127.85</v>
       </c>
+      <c r="X41" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>130.41</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>259.27</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>119.66</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>160.19</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>235.11</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>153.61</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>127.85</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3701,6 +5826,57 @@
       <c r="W42" t="n">
         <v>145.27</v>
       </c>
+      <c r="X42" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>196.63</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>127.11</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>110.14</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>225.84</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>169.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>145.27</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3778,6 +5954,57 @@
       <c r="W43" t="n">
         <v>42.5</v>
       </c>
+      <c r="X43" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>94.81</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>227.58</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>157.03</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>142.94</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>161.79</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>42.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3855,6 +6082,57 @@
       <c r="W44" t="n">
         <v>48.28</v>
       </c>
+      <c r="X44" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>127.02</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>171.82</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>103</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>155.72</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>176.46</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>48.28</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3932,6 +6210,57 @@
       <c r="W45" t="n">
         <v>110.81</v>
       </c>
+      <c r="X45" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>178.31</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>123.31</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>184.77</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>165.32</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>110.81</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -4009,6 +6338,57 @@
       <c r="W46" t="n">
         <v>95.29000000000001</v>
       </c>
+      <c r="X46" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>206.17</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>149.63</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>121.68</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>111.64</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>291.03</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>214.66</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>95.29000000000001</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -4086,6 +6466,57 @@
       <c r="W47" t="n">
         <v>124.57</v>
       </c>
+      <c r="X47" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>140.65</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>325.53</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>182.59</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>39.41</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>234.8</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>240.02</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>108.28</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>124.57</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -4163,6 +6594,57 @@
       <c r="W48" t="n">
         <v>168.17</v>
       </c>
+      <c r="X48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>221.72</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>106.67</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>216.01</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>74.41</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>168.17</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -4240,6 +6722,57 @@
       <c r="W49" t="n">
         <v>164.29</v>
       </c>
+      <c r="X49" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>207.13</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>108.98</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>211.22</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>181.01</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>164.29</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -4317,6 +6850,57 @@
       <c r="W50" t="n">
         <v>227.46</v>
       </c>
+      <c r="X50" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>148.2</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>213.3</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>185.22</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>100.73</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>227.46</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -4394,6 +6978,57 @@
       <c r="W51" t="n">
         <v>67.94</v>
       </c>
+      <c r="X51" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>213.73</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>138.98</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>170.52</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>249.88</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>180.84</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>67.94</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -4471,6 +7106,57 @@
       <c r="W52" t="n">
         <v>172.19</v>
       </c>
+      <c r="X52" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>206.55</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>209.93</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>142.54</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>260.57</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>176.07</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>172.19</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -4548,6 +7234,57 @@
       <c r="W53" t="n">
         <v>255.23</v>
       </c>
+      <c r="X53" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>124.21</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>117.66</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>201.35</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>190.21</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>255.23</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -4625,6 +7362,57 @@
       <c r="W54" t="n">
         <v>214.95</v>
       </c>
+      <c r="X54" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>105.04</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>197.04</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>171.18</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>87.92</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>136.68</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>214.95</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -4702,6 +7490,57 @@
       <c r="W55" t="n">
         <v>229.39</v>
       </c>
+      <c r="X55" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>135.53</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>193.46</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>205.75</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>229.39</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -4779,6 +7618,57 @@
       <c r="W56" t="n">
         <v>172.21</v>
       </c>
+      <c r="X56" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>117.56</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>205.97</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>279.94</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>138.63</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>172.21</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -4856,6 +7746,57 @@
       <c r="W57" t="n">
         <v>336.26</v>
       </c>
+      <c r="X57" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>204.69</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>208.62</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>310.37</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>148.82</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>223.56</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>336.26</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -4933,6 +7874,57 @@
       <c r="W58" t="n">
         <v>302.13</v>
       </c>
+      <c r="X58" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>82.97</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>168.64</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>261.36</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>141.34</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>214.59</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>302.13</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -5010,6 +8002,57 @@
       <c r="W59" t="n">
         <v>179.73</v>
       </c>
+      <c r="X59" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>142.03</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>191.88</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>148.65</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>204.43</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>161.62</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>179.73</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -5087,6 +8130,57 @@
       <c r="W60" t="n">
         <v>223.44</v>
       </c>
+      <c r="X60" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>253.82</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>174.39</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>76.13</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>190.78</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>223.44</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -5164,6 +8258,57 @@
       <c r="W61" t="n">
         <v>215.92</v>
       </c>
+      <c r="X61" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>72.59</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>75.28</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>172.24</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>238.74</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>175.48</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>182.99</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>206.41</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>215.92</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -5241,6 +8386,57 @@
       <c r="W62" t="n">
         <v>268.87</v>
       </c>
+      <c r="X62" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>196.35</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>287.69</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>146.72</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>268.87</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -5318,6 +8514,57 @@
       <c r="W63" t="n">
         <v>330.29</v>
       </c>
+      <c r="X63" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>174.77</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>179.06</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>109.19</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>330.29</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -5395,6 +8642,57 @@
       <c r="W64" t="n">
         <v>268.59</v>
       </c>
+      <c r="X64" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>177.63</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>268.59</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -5472,6 +8770,57 @@
       <c r="W65" t="n">
         <v>231.98</v>
       </c>
+      <c r="X65" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>114.41</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>187.57</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>192.14</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>164.97</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>193.84</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>231.98</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -5549,6 +8898,57 @@
       <c r="W66" t="n">
         <v>259.32</v>
       </c>
+      <c r="X66" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>139.34</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>78.98</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>215.23</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>167.56</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>171.73</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>141.64</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>259.32</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -5626,6 +9026,57 @@
       <c r="W67" t="n">
         <v>278.11</v>
       </c>
+      <c r="X67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>137.71</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>113.06</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>111.42</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>211.13</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>278.11</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -5703,6 +9154,57 @@
       <c r="W68" t="n">
         <v>266.53</v>
       </c>
+      <c r="X68" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>152.35</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>152.64</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>217.66</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>168.82</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>151.83</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>194.07</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>266.53</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -5780,6 +9282,57 @@
       <c r="W69" t="n">
         <v>333.03</v>
       </c>
+      <c r="X69" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>93.68000000000001</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>218.92</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>229.42</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>333.03</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -5857,6 +9410,57 @@
       <c r="W70" t="n">
         <v>148.79</v>
       </c>
+      <c r="X70" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>218.37</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>193.75</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>224.64</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>132.64</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>157.94</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>107.97</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>148.79</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -5934,6 +9538,57 @@
       <c r="W71" t="n">
         <v>194.46</v>
       </c>
+      <c r="X71" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>185.39</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>206.35</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>241.82</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>194.46</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -6011,6 +9666,57 @@
       <c r="W72" t="n">
         <v>125.8</v>
       </c>
+      <c r="X72" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>232.04</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>263.95</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>77.45999999999999</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>132.21</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>125.8</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -6088,6 +9794,57 @@
       <c r="W73" t="n">
         <v>220.66</v>
       </c>
+      <c r="X73" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>174.62</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>103.69</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>201.2</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>220.66</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -6163,6 +9920,57 @@
         <v>209.63</v>
       </c>
       <c r="W74" t="n">
+        <v>271.12</v>
+      </c>
+      <c r="X74" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>141.98</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>151.34</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>246.32</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>172.14</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>130.44</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>209.63</v>
+      </c>
+      <c r="AN74" t="n">
         <v>271.12</v>
       </c>
     </row>
